--- a/客户组件模板/罗克韦尔模板.xlsx
+++ b/客户组件模板/罗克韦尔模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\客户组件模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D16239-199F-4412-B41A-92B9ED13BC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6762453F-E287-4879-B5BB-2CD6BADB3ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
   <si>
     <t>组件模板配置表（极简）</t>
   </si>
@@ -174,9 +174,6 @@
     <t>元素单价</t>
   </si>
   <si>
-    <t>组成件名称</t>
-  </si>
-  <si>
     <t>组成数量</t>
   </si>
   <si>
@@ -193,10 +190,6 @@
   </si>
   <si>
     <t>加工费</t>
-  </si>
-  <si>
-    <t>料件名称</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>净重</t>
@@ -212,6 +205,26 @@
   </si>
   <si>
     <t>组成单位</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>料号</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>单价</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数字输入框</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>料件</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属销售料号</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1034,11 +1047,15 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="12"/>
+      <c r="C4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="E4" s="13"/>
       <c r="F4" s="14"/>
       <c r="G4" s="13"/>
@@ -1056,7 +1073,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1078,7 +1095,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1089,7 +1106,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1100,7 +1117,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1172,7 +1189,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1181,7 +1198,9 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="13"/>
+      <c r="G4" s="13" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="11" t="s">
@@ -1191,7 +1210,7 @@
       <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="13"/>
@@ -1300,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1344,7 +1363,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1353,17 +1372,19 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="13"/>
+      <c r="G4" s="13" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="11" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="13"/>
@@ -1372,7 +1393,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1383,7 +1404,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1391,6 +1412,19 @@
       <c r="E7" s="13"/>
       <c r="F7" s="14"/>
       <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="13" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1455,26 +1489,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>34</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B4" s="12"/>
       <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
+      <c r="D4" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="E4" s="13"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="13"/>
+      <c r="G4" s="13" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="13"/>
+      <c r="D5" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="E5" s="13"/>
       <c r="F5" s="14"/>
       <c r="G5" s="13"/>
@@ -1485,9 +1523,7 @@
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
-      <c r="D6" s="12" t="s">
-        <v>34</v>
-      </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
         <v>34</v>
       </c>
@@ -1496,7 +1532,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1509,7 +1545,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
